--- a/Assets/Document/云熹约定项目文档/12.NE结局/结局统计.xlsx
+++ b/Assets/Document/云熹约定项目文档/12.NE结局/结局统计.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1456,7 +1456,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:A21" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:A23" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
